--- a/4503 JP.xlsx
+++ b/4503 JP.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\shkre\code\models\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Martin Shkreli - DL\models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC6B0BC3-1CD2-4E87-946D-73AC3C524D6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{773E8EC8-72FE-47CA-A15B-345F5B86E086}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-26700" yWindow="540" windowWidth="26490" windowHeight="19650" xr2:uid="{A54D3B08-E225-4A58-B8D9-88B8FEFFB13D}"/>
+    <workbookView xWindow="19210" yWindow="3800" windowWidth="19050" windowHeight="16100" xr2:uid="{A54D3B08-E225-4A58-B8D9-88B8FEFFB13D}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="91">
   <si>
     <t>Price JPY</t>
   </si>
@@ -307,6 +307,9 @@
   </si>
   <si>
     <t>Vyloy</t>
+  </si>
+  <si>
+    <t>Q126</t>
   </si>
 </sst>
 </file>
@@ -863,17 +866,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0DE6F844-253E-42C7-896B-9951B83D0D9E}">
   <dimension ref="B2:L23"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
-    <col min="2" max="2" width="20.28515625" customWidth="1"/>
+    <col min="2" max="2" width="20.26953125" customWidth="1"/>
     <col min="3" max="3" width="11" customWidth="1"/>
-    <col min="4" max="4" width="10.7109375" customWidth="1"/>
-    <col min="10" max="10" width="9.85546875" customWidth="1"/>
-    <col min="11" max="11" width="9.7109375" customWidth="1"/>
+    <col min="4" max="4" width="10.7265625" customWidth="1"/>
+    <col min="10" max="10" width="9.81640625" customWidth="1"/>
+    <col min="11" max="11" width="9.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="2" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B2" s="10" t="s">
         <v>57</v>
       </c>
@@ -891,10 +894,10 @@
         <v>0</v>
       </c>
       <c r="K2" s="1">
-        <v>1792</v>
-      </c>
-    </row>
-    <row r="3" spans="2:12" x14ac:dyDescent="0.2">
+        <v>2202</v>
+      </c>
+    </row>
+    <row r="3" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B3" s="5" t="s">
         <v>58</v>
       </c>
@@ -912,13 +915,13 @@
         <v>1</v>
       </c>
       <c r="K3" s="1">
-        <v>1822.6130000000001</v>
+        <v>1791.105329</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="4" spans="2:12" x14ac:dyDescent="0.2">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="4" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B4" s="5" t="s">
         <v>70</v>
       </c>
@@ -935,11 +938,11 @@
       </c>
       <c r="K4" s="1">
         <f>+K2*K3</f>
-        <v>3266122.4960000003</v>
+        <v>3944013.9344580001</v>
       </c>
       <c r="L4" s="2"/>
     </row>
-    <row r="5" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="5" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B5" s="5" t="s">
         <v>71</v>
       </c>
@@ -953,13 +956,14 @@
         <v>3</v>
       </c>
       <c r="K5" s="1">
-        <v>471543</v>
+        <f>138296+281605+9572+20297</f>
+        <v>449770</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="6" spans="2:12" x14ac:dyDescent="0.2">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="6" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B6" s="5" t="s">
         <v>73</v>
       </c>
@@ -975,13 +979,14 @@
         <v>4</v>
       </c>
       <c r="K6" s="1">
-        <v>1202652</v>
+        <f>320000+89082+22342+245952</f>
+        <v>677376</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="7" spans="2:12" x14ac:dyDescent="0.2">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="7" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B7" s="5" t="s">
         <v>53</v>
       </c>
@@ -996,10 +1001,10 @@
       </c>
       <c r="K7" s="1">
         <f>+K4-K5+K6</f>
-        <v>3997231.4960000003</v>
-      </c>
-    </row>
-    <row r="8" spans="2:12" x14ac:dyDescent="0.2">
+        <v>4171619.9344580001</v>
+      </c>
+    </row>
+    <row r="8" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B8" s="5" t="s">
         <v>65</v>
       </c>
@@ -1011,7 +1016,7 @@
       <c r="H8" s="16"/>
       <c r="K8" s="1"/>
     </row>
-    <row r="9" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="9" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B9" s="5" t="s">
         <v>66</v>
       </c>
@@ -1023,7 +1028,7 @@
       <c r="H9" s="16"/>
       <c r="K9" s="1"/>
     </row>
-    <row r="10" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="10" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B10" s="5" t="s">
         <v>67</v>
       </c>
@@ -1035,7 +1040,7 @@
       <c r="H10" s="16"/>
       <c r="K10" s="1"/>
     </row>
-    <row r="11" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="11" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B11" s="5" t="s">
         <v>68</v>
       </c>
@@ -1047,7 +1052,7 @@
       <c r="H11" s="16"/>
       <c r="K11" s="1"/>
     </row>
-    <row r="12" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="12" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B12" s="5" t="s">
         <v>69</v>
       </c>
@@ -1059,7 +1064,7 @@
       <c r="H12" s="16"/>
       <c r="K12" s="1"/>
     </row>
-    <row r="13" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="13" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B13" s="7" t="s">
         <v>64</v>
       </c>
@@ -1070,7 +1075,7 @@
       <c r="G13" s="17"/>
       <c r="H13" s="18"/>
     </row>
-    <row r="14" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="14" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B14" s="10"/>
       <c r="C14" s="11"/>
       <c r="D14" s="11"/>
@@ -1079,7 +1084,7 @@
       <c r="G14" s="11"/>
       <c r="H14" s="12"/>
     </row>
-    <row r="15" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="15" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B15" s="5" t="s">
         <v>75</v>
       </c>
@@ -1091,7 +1096,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="16" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="16" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B16" s="5" t="s">
         <v>77</v>
       </c>
@@ -1100,11 +1105,11 @@
       </c>
       <c r="H16" s="6"/>
     </row>
-    <row r="17" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="17" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B17" s="5"/>
       <c r="H17" s="6"/>
     </row>
-    <row r="18" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="18" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B18" s="5" t="s">
         <v>55</v>
       </c>
@@ -1113,23 +1118,23 @@
       </c>
       <c r="H18" s="6"/>
     </row>
-    <row r="19" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="19" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B19" s="5"/>
       <c r="H19" s="6"/>
     </row>
-    <row r="20" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="20" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B20" s="5"/>
       <c r="H20" s="6"/>
     </row>
-    <row r="21" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="21" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B21" s="5"/>
       <c r="H21" s="6"/>
     </row>
-    <row r="22" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="22" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B22" s="5"/>
       <c r="H22" s="6"/>
     </row>
-    <row r="23" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="23" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B23" s="7"/>
       <c r="C23" s="8"/>
       <c r="D23" s="8"/>
@@ -1147,25 +1152,25 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C752DD14-34D2-4EF9-B844-A3F2BC725485}">
   <dimension ref="A1:V47"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.28515625" customWidth="1"/>
-    <col min="3" max="4" width="9.140625" style="2"/>
-    <col min="5" max="5" width="10.140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="8" width="9.140625" style="2"/>
-    <col min="9" max="9" width="10.140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="9.140625" style="2"/>
-    <col min="13" max="13" width="10.140625" bestFit="1" customWidth="1"/>
-    <col min="15" max="22" width="9.5703125" customWidth="1"/>
+    <col min="2" max="2" width="12.26953125" customWidth="1"/>
+    <col min="3" max="4" width="9.1796875" style="2"/>
+    <col min="5" max="5" width="10.1796875" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="8" width="9.1796875" style="2"/>
+    <col min="9" max="9" width="10.1796875" style="2" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.1796875" style="2"/>
+    <col min="13" max="13" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="15" max="22" width="9.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A1" s="23" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:22" s="19" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:22" s="19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="C2" s="20">
         <v>44012</v>
       </c>
@@ -1235,7 +1240,7 @@
         <v>45747</v>
       </c>
     </row>
-    <row r="3" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:22" x14ac:dyDescent="0.25">
       <c r="C3" s="2" t="s">
         <v>8</v>
       </c>
@@ -1297,7 +1302,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="4" spans="1:22" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:22" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B4" s="1" t="s">
         <v>49</v>
       </c>
@@ -1327,7 +1332,7 @@
         <v>224200</v>
       </c>
     </row>
-    <row r="5" spans="1:22" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:22" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B5" s="1" t="s">
         <v>50</v>
       </c>
@@ -1357,7 +1362,7 @@
         <v>38400</v>
       </c>
     </row>
-    <row r="6" spans="1:22" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:22" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B6" s="1" t="s">
         <v>87</v>
       </c>
@@ -1380,7 +1385,7 @@
         <v>12700</v>
       </c>
     </row>
-    <row r="7" spans="1:22" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:22" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B7" s="1" t="s">
         <v>88</v>
       </c>
@@ -1403,7 +1408,7 @@
         <v>6600</v>
       </c>
     </row>
-    <row r="8" spans="1:22" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:22" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B8" s="1" t="s">
         <v>89</v>
       </c>
@@ -1426,7 +1431,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="9" spans="1:22" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:22" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B9" s="1" t="s">
         <v>51</v>
       </c>
@@ -1456,7 +1461,7 @@
         <v>17300</v>
       </c>
     </row>
-    <row r="10" spans="1:22" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:22" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B10" s="1" t="s">
         <v>52</v>
       </c>
@@ -1480,7 +1485,7 @@
       </c>
       <c r="N10" s="3"/>
     </row>
-    <row r="11" spans="1:22" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:22" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B11" s="1" t="s">
         <v>53</v>
       </c>
@@ -1510,7 +1515,7 @@
         <v>53900</v>
       </c>
     </row>
-    <row r="12" spans="1:22" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:22" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B12" s="1" t="s">
         <v>54</v>
       </c>
@@ -1540,13 +1545,13 @@
         <v>46100</v>
       </c>
     </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:22" x14ac:dyDescent="0.25">
       <c r="K13" s="2"/>
       <c r="L13" s="2"/>
       <c r="M13" s="2"/>
       <c r="N13" s="2"/>
     </row>
-    <row r="14" spans="1:22" s="21" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:22" s="21" customFormat="1" ht="13" x14ac:dyDescent="0.3">
       <c r="B14" s="21" t="s">
         <v>7</v>
       </c>
@@ -1584,7 +1589,7 @@
         <v>473124</v>
       </c>
     </row>
-    <row r="15" spans="1:22" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:22" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B15" s="1" t="s">
         <v>20</v>
       </c>
@@ -1622,7 +1627,7 @@
         <v>91136</v>
       </c>
     </row>
-    <row r="16" spans="1:22" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:22" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B16" s="1" t="s">
         <v>21</v>
       </c>
@@ -1664,7 +1669,7 @@
         <v>381988</v>
       </c>
     </row>
-    <row r="17" spans="2:19" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="2:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B17" s="1" t="s">
         <v>22</v>
       </c>
@@ -1702,7 +1707,7 @@
         <v>206877</v>
       </c>
     </row>
-    <row r="18" spans="2:19" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="2:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B18" s="1" t="s">
         <v>23</v>
       </c>
@@ -1740,7 +1745,7 @@
         <v>86821</v>
       </c>
     </row>
-    <row r="19" spans="2:19" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="2:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B19" s="1" t="s">
         <v>24</v>
       </c>
@@ -1778,11 +1783,11 @@
         <v>232774</v>
       </c>
       <c r="S19" s="1">
-        <f t="shared" ref="P19:S19" si="1">+S17+S18</f>
+        <f t="shared" ref="S19" si="1">+S17+S18</f>
         <v>293698</v>
       </c>
     </row>
-    <row r="20" spans="2:19" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="2:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B20" s="1" t="s">
         <v>25</v>
       </c>
@@ -1820,11 +1825,11 @@
         <v>73269</v>
       </c>
       <c r="S20" s="1">
-        <f t="shared" ref="P20:S20" si="3">+S16-S19</f>
+        <f t="shared" ref="S20" si="3">+S16-S19</f>
         <v>88290</v>
       </c>
     </row>
-    <row r="21" spans="2:19" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="2:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B21" s="1" t="s">
         <v>26</v>
       </c>
@@ -1859,7 +1864,7 @@
         <v>1056</v>
       </c>
     </row>
-    <row r="22" spans="2:19" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="2:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B22" s="1" t="s">
         <v>27</v>
       </c>
@@ -1897,11 +1902,11 @@
         <v>73107</v>
       </c>
       <c r="S22" s="1">
-        <f t="shared" ref="P22:S22" si="4">+S20+S21</f>
+        <f t="shared" ref="S22" si="4">+S20+S21</f>
         <v>89346</v>
       </c>
     </row>
-    <row r="23" spans="2:19" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="2:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B23" s="1" t="s">
         <v>28</v>
       </c>
@@ -1939,7 +1944,7 @@
         <v>13721</v>
       </c>
     </row>
-    <row r="24" spans="2:19" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="2:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B24" s="1" t="s">
         <v>29</v>
       </c>
@@ -1981,7 +1986,7 @@
         <v>75625</v>
       </c>
     </row>
-    <row r="26" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="26" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B26" s="1" t="s">
         <v>47</v>
       </c>
@@ -2002,7 +2007,7 @@
         <v>0.26169764527054062</v>
       </c>
     </row>
-    <row r="27" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="27" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B27" s="1" t="s">
         <v>48</v>
       </c>
@@ -2039,7 +2044,7 @@
         <v>0.80737396538750938</v>
       </c>
     </row>
-    <row r="29" spans="2:19" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="2:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B29" s="1" t="s">
         <v>30</v>
       </c>
@@ -2064,7 +2069,7 @@
         <v>471543</v>
       </c>
     </row>
-    <row r="30" spans="2:19" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="2:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B30" s="1" t="s">
         <v>31</v>
       </c>
@@ -2087,7 +2092,7 @@
         <v>45972</v>
       </c>
     </row>
-    <row r="31" spans="2:19" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="2:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B31" s="1" t="s">
         <v>34</v>
       </c>
@@ -2111,7 +2116,7 @@
         <v>66515</v>
       </c>
     </row>
-    <row r="32" spans="2:19" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="2:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B32" s="1" t="s">
         <v>33</v>
       </c>
@@ -2135,7 +2140,7 @@
         <v>609708</v>
       </c>
     </row>
-    <row r="33" spans="2:19" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B33" s="1" t="s">
         <v>32</v>
       </c>
@@ -2157,7 +2162,7 @@
         <v>256045</v>
       </c>
     </row>
-    <row r="34" spans="2:19" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B34" s="1" t="s">
         <v>35</v>
       </c>
@@ -2179,7 +2184,7 @@
         <v>29214</v>
       </c>
     </row>
-    <row r="35" spans="2:19" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B35" s="1" t="s">
         <v>37</v>
       </c>
@@ -2204,7 +2209,7 @@
         <v>1946831</v>
       </c>
     </row>
-    <row r="36" spans="2:19" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="2:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B36" s="1" t="s">
         <v>38</v>
       </c>
@@ -2226,7 +2231,7 @@
         <v>309686</v>
       </c>
     </row>
-    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B37" s="1" t="s">
         <v>36</v>
       </c>
@@ -2243,7 +2248,7 @@
         <v>3735514</v>
       </c>
     </row>
-    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B39" s="1" t="s">
         <v>40</v>
       </c>
@@ -2257,7 +2262,7 @@
         <v>1676442</v>
       </c>
     </row>
-    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B40" s="1" t="s">
         <v>39</v>
       </c>
@@ -2271,7 +2276,7 @@
         <v>503002</v>
       </c>
     </row>
-    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B41" s="1" t="s">
         <v>41</v>
       </c>
@@ -2288,7 +2293,7 @@
         <v>1202652</v>
       </c>
     </row>
-    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B42" s="1" t="s">
         <v>42</v>
       </c>
@@ -2302,7 +2307,7 @@
         <v>24126</v>
       </c>
     </row>
-    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B43" s="1" t="s">
         <v>28</v>
       </c>
@@ -2316,7 +2321,7 @@
         <v>74977</v>
       </c>
     </row>
-    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B44" s="1" t="s">
         <v>43</v>
       </c>
@@ -2329,7 +2334,7 @@
         <v>181612</v>
       </c>
     </row>
-    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B45" s="1" t="s">
         <v>44</v>
       </c>
@@ -2344,7 +2349,7 @@
         <v>47327</v>
       </c>
     </row>
-    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B46" s="1" t="s">
         <v>46</v>
       </c>
@@ -2358,7 +2363,7 @@
         <v>25377</v>
       </c>
     </row>
-    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B47" s="1" t="s">
         <v>45</v>
       </c>
